--- a/stories/arbres/ATOM-JEU.BAL.001-02.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tom et maman sont dans le jardin. L'herbe est douce. Maman pose deux sacs. Elle dit : voici l'espace du jeu. Tom reste dans l'espace du jeu. Maman donne le ballon. Tom le sent. Il est un peu lourd. Maman dit : on va passer le ballon. Chacun a son tour. Tom passe le ballon à maman. Maman l'attrape. C'est le tour de maman. Maman passe le ballon. Tom attend. Puis c'est son tour. Tom passe encore. Une abeille passe. Tom reste dans l'espace. Il attend. Il passe. Parce qu'il attend son tour, le jeu reste doux. Maman dit : bien joué.</t>
+          <t>Tom et maman sont dans le jardin. L'herbe est douce. Maman pose deux sacs. Voici l'espace du jeu. Tom reste dans l'espace du jeu. Maman donne le ballon. Tom le sent. Il est un peu lourd. On va passer le ballon. Chacun a son tour. Tom passe le ballon à maman. Maman l'attrape. C'est le tour de maman. Maman passe le ballon. Tom attend. Puis c'est son tour. Tom passe encore. Une abeille passe. Tom reste dans l'espace. Il attend. Il passe. Parce qu'il attend son tour, le jeu reste doux. Bien joué.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Tom et maman sont dans le jardin. L'herbe est douce. Maman pose deux sacs.
+narrateur|Voici l'espace du jeu.
+narrateur|Tom reste dans l'espace du jeu. Maman donne le ballon. Tom le sent. Il est un peu lourd.
+maman|On va passer le ballon. Chacun a son tour.
+narrateur|Tom passe le ballon à maman. Maman l'attrape. C'est le tour de maman. Maman passe le ballon. Tom attend. Puis c'est son tour. Tom passe encore. Une abeille passe. Tom reste dans l'espace. Il attend. Il passe. Parce qu'il attend son tour, le jeu reste doux.
+maman|Bien joué.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a le ballon. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range le ballon. Tom boit de l'eau. Ils rentrent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-02.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,11 @@
 maman|Bien joué.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1508,7 @@
           <t>narrateur|Tom a le ballon. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1680,7 @@
           <t>narrateur|Tom a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1844,7 @@
           <t>narrateur|Maman range le ballon. Tom boit de l'eau. Ils rentrent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2055,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.BAL.001-02.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tom passe le ballon</t>
+          <t>Aniss passe le ballon</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>L'arrosoir laisse une goutte. Aniss et maman se passent le ballon dans l'espace du jeu. Papa arrose. Parce qu'il attend, le jeu reste doux.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tom et maman sont dans le jardin. L'herbe est douce. Maman pose deux sacs. Voici l'espace du jeu. Tom reste dans l'espace du jeu. Maman donne le ballon. Tom le sent. Il est un peu lourd. On va passer le ballon. Chacun a son tour. Tom passe le ballon à maman. Maman l'attrape. C'est le tour de maman. Maman passe le ballon. Tom attend. Puis c'est son tour. Tom passe encore. Une abeille passe. Tom reste dans l'espace. Il attend. Il passe. Parce qu'il attend son tour, le jeu reste doux. Bien joué.</t>
+          <t>L'arrosoir laisse une goutte sur une feuille. La goutte glisse, puis tombe. Des tomates pendent, bien rouges. Ça sent la terre humide. Une abeille visite une fleur. Le linge sèche sur la corde. Papa tient l'arrosoir, plus loin. Aniss, tu as vu la goutte ? Oui, maman. Elle est tombée. La feuille est toute brillante. J'arrose les tomates. En ce moment, maman pose deux sacs. Voici l'espace du jeu. Aniss reste dans l'espace du jeu. Maman donne le ballon. Le ballon est un peu lourd. Il sent le caoutchouc chaud. Il est lourd. On va passer le ballon. Chacun a son tour. Aniss passe le ballon à maman. Maman l'attrape. C'est mon tour. Maman passe le ballon. Aniss attend. Puis c'est son tour. Aniss passe encore. L'abeille passe près de la corde. Aniss reste dans l'espace. Il attend. Il passe. Parce qu'il attend son tour, le jeu reste doux. Bien joué. Chacun a son tour. Chacun a son tour. Tu restes dans l'espace ? Oui, papa. Bravo, Aniss. Tu as fait du bon travail. Encore un passage ? Oui. Aniss passe le ballon. Maman le rend. La goutte a séché sur la terre. Les tomates restent rouges.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,52 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Tom et maman sont dans le jardin. L'herbe est douce. Maman pose deux sacs.
-narrateur|Voici l'espace du jeu.
-narrateur|Tom reste dans l'espace du jeu. Maman donne le ballon. Tom le sent. Il est un peu lourd.
-maman|On va passer le ballon. Chacun a son tour.
-narrateur|Tom passe le ballon à maman. Maman l'attrape. C'est le tour de maman. Maman passe le ballon. Tom attend. Puis c'est son tour. Tom passe encore. Une abeille passe. Tom reste dans l'espace. Il attend. Il passe. Parce qu'il attend son tour, le jeu reste doux.
-maman|Bien joué.</t>
+          <t>narrateur|L'arrosoir laisse une goutte sur une feuille.
+narrateur|La goutte glisse, puis tombe.
+narrateur|Des tomates pendent, bien rouges.
+narrateur|Ça sent la terre humide.
+narrateur|Une abeille visite une fleur.
+narrateur|Le linge sèche sur la corde.
+narrateur|Papa tient l'arrosoir, plus loin.
+maman|Aniss, tu as vu la goutte ?
+enfant-m|Oui, maman.
+enfant-m|Elle est tombée.
+maman|La feuille est toute brillante.
+papa|J'arrose les tomates.
+narrateur|En ce moment, maman pose deux sacs.
+maman|Voici l'espace du jeu.
+narrateur|Aniss reste dans l'espace du jeu.
+narrateur|Maman donne le ballon.
+narrateur|Le ballon est un peu lourd.
+narrateur|Il sent le caoutchouc chaud.
+enfant-m|Il est lourd.
+maman|On va passer le ballon.
+maman|Chacun a son tour.
+narrateur|Aniss passe le ballon à maman.
+narrateur|Maman l'attrape.
+maman|C'est mon tour.
+narrateur|Maman passe le ballon.
+narrateur|Aniss attend.
+narrateur|Puis c'est son tour.
+narrateur|Aniss passe encore.
+narrateur|L'abeille passe près de la corde.
+narrateur|Aniss reste dans l'espace.
+narrateur|Il attend.
+narrateur|Il passe.
+narrateur|Parce qu'il attend son tour, le jeu reste doux.
+maman|Bien joué.
+maman|Chacun a son tour.
+enfant-m|Chacun a son tour.
+papa|Tu restes dans l'espace ?
+enfant-m|Oui, papa.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Encore un passage ?
+enfant-m|Oui.
+narrateur|Aniss passe le ballon.
+narrateur|Maman le rend.
+narrateur|La goutte a séché sur la terre.
+narrateur|Les tomates restent rouges.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1349,7 +1401,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tom a le ballon. Que fait-il ?</t>
+          <t>Aniss a le ballon. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1505,10 +1557,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Tom a le ballon. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Aniss a le ballon.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1533,7 +1585,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu.</t>
+          <t>Aniss a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu. Tu as attendu ton tour ? Oui, maman. Bravo. Parce que tu attends, le jeu reste doux. Tu es resté dans l'espace ? Oui, papa. Bravo. Le ballon est un peu poussiéreux. L'herbe sent encore la terre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1677,10 +1729,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Tom a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Aniss a passé le ballon.
+narrateur|Il a attendu son tour.
+narrateur|Il est resté dans l'espace du jeu.
+maman|Tu as attendu ton tour ?
+enfant-m|Oui, maman.
+maman|Bravo.
+maman|Parce que tu attends, le jeu reste doux.
+papa|Tu es resté dans l'espace ?
+enfant-m|Oui, papa.
+papa|Bravo.
+narrateur|Le ballon est un peu poussiéreux.
+narrateur|L'herbe sent encore la terre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1705,7 +1767,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le ballon. Tom boit de l'eau. Ils rentrent.</t>
+          <t>Maman range le ballon. Tu bois de l'eau ? Oui, maman. Aniss boit de l'eau. La gourde sent le citron. Je pose l'arrosoir. On rentre ? Oui. Bravo. Ils rentrent. L'arrosoir reste près des tomates.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1841,10 +1903,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range le ballon. Tom boit de l'eau. Ils rentrent.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Maman range le ballon.
+maman|Tu bois de l'eau ?
+enfant-m|Oui, maman.
+narrateur|Aniss boit de l'eau.
+narrateur|La gourde sent le citron.
+papa|Je pose l'arrosoir.
+maman|On rentre ?
+enfant-m|Oui.
+maman|Bravo.
+narrateur|Ils rentrent.
+narrateur|L'arrosoir reste près des tomates.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1869,7 +1940,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le linge bouge un peu. Tu as passé le ballon. Chacun a son tour. Dans l'espace du jeu. Oui, maman. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2009,10 +2080,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le linge bouge un peu.
+maman|Tu as passé le ballon.
+maman|Chacun a son tour.
+papa|Dans l'espace du jeu.
+enfant-m|Oui, maman.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2031,7 +2106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2144,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-02.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L'arrosoir laisse une goutte sur une feuille. La goutte glisse, puis tombe. Des tomates pendent, bien rouges. Ça sent la terre humide. Une abeille visite une fleur. Le linge sèche sur la corde. Papa tient l'arrosoir, plus loin. Aniss, tu as vu la goutte ? Oui, maman. Elle est tombée. La feuille est toute brillante. J'arrose les tomates. En ce moment, maman pose deux sacs. Voici l'espace du jeu. Aniss reste dans l'espace du jeu. Maman donne le ballon. Le ballon est un peu lourd. Il sent le caoutchouc chaud. Il est lourd. On va passer le ballon. Chacun a son tour. Aniss passe le ballon à maman. Maman l'attrape. C'est mon tour. Maman passe le ballon. Aniss attend. Puis c'est son tour. Aniss passe encore. L'abeille passe près de la corde. Aniss reste dans l'espace. Il attend. Il passe. Parce qu'il attend son tour, le jeu reste doux. Bien joué. Chacun a son tour. Chacun a son tour. Tu restes dans l'espace ? Oui, papa. Bravo, Aniss. Tu as fait du bon travail. Encore un passage ? Oui. Aniss passe le ballon. Maman le rend. La goutte a séché sur la terre. Les tomates restent rouges.</t>
+          <t>L'arrosoir laisse une goutte sur une feuille. La goutte glisse, puis tombe. Des tomates pendent, bien rouges. Ça sent la terre humide. Une abeille visite une fleur. Le linge sèche sur la corde. Un pot de basilic sent fort. Papa tient l'arrosoir, plus loin. L'eau fait un bruit fin. Aniss, tu as vu la goutte ? Oui, maman. Elle est tombée. La feuille est toute brillante. J'arrose les tomates. En ce moment, maman pose deux sacs. Voici l'espace du jeu. Aniss reste dans l'espace du jeu. Maman donne le ballon. Le ballon est un peu lourd. Il sent le caoutchouc chaud. Il est lourd. On va passer le ballon. Chacun a son tour. Aniss passe le ballon à maman. Maman l'attrape. C'est mon tour. Maman passe le ballon. Aniss attend. Puis c'est son tour. Aniss passe encore. L'abeille passe près de la corde. Aniss reste dans l'espace. Il attend. Il passe. Parce qu'il attend son tour, le jeu reste doux. Bien joué. Chacun a son tour. Chacun a son tour. Tu restes dans l'espace ? Oui, papa. Bravo, Aniss. Encore un passage ? Oui. Aniss passe le ballon. Maman le rend. La goutte a séché sur la terre. Les tomates restent rouges. Le basilic sent fort. Oui, papa. On reste dans l'espace. Le linge bouge encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tom et maman sont dans le jardin. L'herbe est douce. Maman pose deux sacs. Elle dit : voici l'espace du jeu. Tom reste dans l'espace du jeu. Maman donne le ballon. Tom le sent. Il est un peu lourd. Maman dit : on va &lt;emphasis level="moderate"&gt;passer&lt;/emphasis&gt; le ballon. Chacun a son tour. Tom passe le ballon à maman. Maman l'attrape. C'est le tour de maman. Maman passe le ballon. Tom attend. Puis c'est son tour. Tom passe encore. Une abeille passe. Tom reste dans l'espace. Il attend. Il passe. Parce qu'il attend son tour, le jeu reste doux. Maman dit : bien joué.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'arrosoir laisse une goutte sur une feuille. La goutte glisse, puis tombe. Des tomates pendent, bien rouges. Ça sent la terre humide. Une abeille visite une fleur. Le linge sèche sur la corde. Un pot de basilic sent fort. Papa tient l'arrosoir, plus loin. L'eau fait un bruit fin. Aniss, tu as vu la goutte ? Oui, maman. Elle est tombée. La feuille est toute brillante. J'arrose les tomates. En ce moment, maman pose deux sacs. Voici l'espace du jeu. Aniss reste dans l'espace du jeu. Maman donne le ballon. Le ballon est un peu lourd. Il sent le caoutchouc chaud. Il est lourd. On va passer le ballon. Chacun a son tour. Aniss passe le ballon à maman. Maman l'attrape. C'est mon tour. Maman passe le ballon. Aniss attend. Puis c'est son tour. Aniss passe encore. L'abeille passe près de la corde. Aniss reste dans l'espace. Il attend. Il passe. Parce qu'il attend son tour, le jeu reste doux. Bien joué. Chacun a son tour. Chacun a son tour. Tu restes dans l'espace ? Oui, papa. Bravo, Aniss. Encore un passage ? Oui. Aniss passe le ballon. Maman le rend. La goutte a séché sur la terre. Les tomates restent rouges. Le basilic sent fort. Oui, papa. On reste dans l'espace. Le linge bouge encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1330,7 +1330,9 @@
 narrateur|Ça sent la terre humide.
 narrateur|Une abeille visite une fleur.
 narrateur|Le linge sèche sur la corde.
+narrateur|Un pot de basilic sent fort.
 narrateur|Papa tient l'arrosoir, plus loin.
+narrateur|L'eau fait un bruit fin.
 maman|Aniss, tu as vu la goutte ?
 enfant-m|Oui, maman.
 enfant-m|Elle est tombée.
@@ -1363,13 +1365,16 @@
 papa|Tu restes dans l'espace ?
 enfant-m|Oui, papa.
 maman|Bravo, Aniss.
-maman|Tu as fait du bon travail.
 papa|Encore un passage ?
 enfant-m|Oui.
 narrateur|Aniss passe le ballon.
 narrateur|Maman le rend.
 narrateur|La goutte a séché sur la terre.
-narrateur|Les tomates restent rouges.</t>
+narrateur|Les tomates restent rouges.
+papa|Le basilic sent fort.
+enfant-m|Oui, papa.
+maman|On reste dans l'espace.
+narrateur|Le linge bouge encore.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1406,7 +1411,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Tom a le ballon. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a le ballon. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1585,12 +1590,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu. Tu as attendu ton tour ? Oui, maman. Bravo. Parce que tu attends, le jeu reste doux. Tu es resté dans l'espace ? Oui, papa. Bravo. Le ballon est un peu poussiéreux. L'herbe sent encore la terre.</t>
+          <t>Aniss a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu. Tu as attendu ton tour ? Oui, maman. Bravo. Parce que tu attends, le jeu reste doux. Tu es resté dans l'espace ? Oui, papa. Bravo. Le ballon est un peu poussiéreux. L'herbe sent encore la terre. On reprend un tour ? Oui, maman. Aniss attend. Puis il passe. Bien joué.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tom a passé le ballon. Il a attendu son &lt;emphasis level="moderate"&gt;tour&lt;/emphasis&gt;. Il est resté dans l'espace du jeu.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu. Tu as attendu ton tour ? Oui, maman. Bravo. Parce que tu attends, le jeu reste doux. Tu es resté dans l'espace ? Oui, papa. Bravo. Le ballon est un peu poussiéreux. L'herbe sent encore la terre. On reprend un tour ? Oui, maman. Aniss attend. Puis il passe. Bien joué.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1740,7 +1745,12 @@
 enfant-m|Oui, papa.
 papa|Bravo.
 narrateur|Le ballon est un peu poussiéreux.
-narrateur|L'herbe sent encore la terre.</t>
+narrateur|L'herbe sent encore la terre.
+maman|On reprend un tour ?
+enfant-m|Oui, maman.
+narrateur|Aniss attend.
+narrateur|Puis il passe.
+papa|Bien joué.</t>
         </is>
       </c>
     </row>
@@ -1767,12 +1777,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le ballon. Tu bois de l'eau ? Oui, maman. Aniss boit de l'eau. La gourde sent le citron. Je pose l'arrosoir. On rentre ? Oui. Bravo. Ils rentrent. L'arrosoir reste près des tomates.</t>
+          <t>Maman range le ballon. Tu bois de l'eau ? Oui, maman. Aniss boit de l'eau. La gourde sent le citron. Je pose l'arrosoir. On rentre ? Oui. Bravo. Ils rentrent. L'arrosoir reste près des tomates. Les tomates sont belles. Elles sont rouges.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range le ballon. Tom boit de l'eau. Ils rentrent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman range le ballon. Tu bois de l'eau ? Oui, maman. Aniss boit de l'eau. La gourde sent le citron. Je pose l'arrosoir. On rentre ? Oui. Bravo. Ils rentrent. L'arrosoir reste près des tomates. Les tomates sont belles. Elles sont rouges.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1913,7 +1923,9 @@
 enfant-m|Oui.
 maman|Bravo.
 narrateur|Ils rentrent.
-narrateur|L'arrosoir reste près des tomates.</t>
+narrateur|L'arrosoir reste près des tomates.
+papa|Les tomates sont belles.
+enfant-m|Elles sont rouges.</t>
         </is>
       </c>
     </row>
@@ -1940,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le linge bouge un peu. Tu as passé le ballon. Chacun a son tour. Dans l'espace du jeu. Oui, maman. L'histoire est finie.</t>
+          <t>Le linge bouge un peu. Tu as passé le ballon. Chacun a son tour. Dans l'espace du jeu. Oui, maman.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le linge bouge un peu. Tu as passé le ballon. Chacun a son tour. Dans l'espace du jeu. Oui, maman.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2084,8 +2096,7 @@
 maman|Tu as passé le ballon.
 maman|Chacun a son tour.
 papa|Dans l'espace du jeu.
-enfant-m|Oui, maman.
-narrateur|L'histoire est finie.</t>
+enfant-m|Oui, maman.</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2151,6 +2162,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-02.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>jardin, arrosoir, tomates, deux sacs</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tom, maman</t>
+          <t>Aniss, maman, papa</t>
         </is>
       </c>
     </row>
